--- a/artfynd/A 54875-2019 artfynd.xlsx
+++ b/artfynd/A 54875-2019 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125681044</v>
+        <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105376</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221423</v>
+        <v>221141</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>rikligt förvildad från trädgårdskompost</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125681081</v>
+        <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105853</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>221423</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -867,7 +852,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ung planta</t>
+          <t>rikligt förvildad från trädgårdskompost</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125681019</v>
+        <v>125680996</v>
       </c>
       <c r="B4" t="n">
-        <v>105205</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221141</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1006,37 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125680994</v>
+        <v>125680976</v>
       </c>
       <c r="B5" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,12 +1065,23 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1113,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125680976</v>
+        <v>125680994</v>
       </c>
       <c r="B6" t="n">
-        <v>91219</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5321</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1197,23 +1178,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1231,37 +1201,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125680996</v>
+        <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>58026</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103037</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1307,6 +1272,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ung planta</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 54875-2019 artfynd.xlsx
+++ b/artfynd/A 54875-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105260</v>
+        <v>105267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105431</v>
+        <v>105438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>125680976</v>
       </c>
       <c r="B5" t="n">
-        <v>91273</v>
+        <v>91280</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105908</v>
+        <v>105915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54875-2019 artfynd.xlsx
+++ b/artfynd/A 54875-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105267</v>
+        <v>105270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105438</v>
+        <v>105441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>125680996</v>
       </c>
       <c r="B4" t="n">
-        <v>58044</v>
+        <v>58045</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>125680976</v>
       </c>
       <c r="B5" t="n">
-        <v>91280</v>
+        <v>91281</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>125680994</v>
       </c>
       <c r="B6" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105915</v>
+        <v>105918</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54875-2019 artfynd.xlsx
+++ b/artfynd/A 54875-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105270</v>
+        <v>105274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105441</v>
+        <v>105445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125680996</v>
+        <v>125680976</v>
       </c>
       <c r="B4" t="n">
-        <v>58045</v>
+        <v>91285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,12 +963,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -986,32 +997,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125680976</v>
+        <v>125680996</v>
       </c>
       <c r="B5" t="n">
-        <v>91281</v>
+        <v>58045</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5321</v>
+        <v>103037</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,23 +1076,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105918</v>
+        <v>105922</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54875-2019 artfynd.xlsx
+++ b/artfynd/A 54875-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105274</v>
+        <v>105275</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105445</v>
+        <v>105446</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125680976</v>
+        <v>125680996</v>
       </c>
       <c r="B4" t="n">
-        <v>91285</v>
+        <v>58045</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,23 +963,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -997,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125680996</v>
+        <v>125680976</v>
       </c>
       <c r="B5" t="n">
-        <v>58045</v>
+        <v>91285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103037</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,12 +1065,23 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105922</v>
+        <v>105923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54875-2019 artfynd.xlsx
+++ b/artfynd/A 54875-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105275</v>
+        <v>105277</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105446</v>
+        <v>105448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125680996</v>
+        <v>125680976</v>
       </c>
       <c r="B4" t="n">
-        <v>58045</v>
+        <v>91287</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,12 +963,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -986,32 +997,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125680976</v>
+        <v>125680996</v>
       </c>
       <c r="B5" t="n">
-        <v>91285</v>
+        <v>58046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5321</v>
+        <v>103037</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,23 +1076,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1102,7 +1102,7 @@
         <v>125680994</v>
       </c>
       <c r="B6" t="n">
-        <v>58130</v>
+        <v>58131</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105923</v>
+        <v>105925</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54875-2019 artfynd.xlsx
+++ b/artfynd/A 54875-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105277</v>
+        <v>105279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105448</v>
+        <v>105450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125680976</v>
+        <v>125680996</v>
       </c>
       <c r="B4" t="n">
-        <v>91287</v>
+        <v>58046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,23 +963,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -997,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125680996</v>
+        <v>125680976</v>
       </c>
       <c r="B5" t="n">
-        <v>58046</v>
+        <v>91289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103037</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,12 +1065,23 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105925</v>
+        <v>105927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54875-2019 artfynd.xlsx
+++ b/artfynd/A 54875-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105279</v>
+        <v>105283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105450</v>
+        <v>105454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125680996</v>
+        <v>125680976</v>
       </c>
       <c r="B4" t="n">
-        <v>58046</v>
+        <v>91291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,12 +963,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -986,32 +997,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125680976</v>
+        <v>125680996</v>
       </c>
       <c r="B5" t="n">
-        <v>91289</v>
+        <v>58046</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5321</v>
+        <v>103037</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,23 +1076,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105927</v>
+        <v>105931</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54875-2019 artfynd.xlsx
+++ b/artfynd/A 54875-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105283</v>
+        <v>105296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105454</v>
+        <v>105467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>125680976</v>
       </c>
       <c r="B4" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>125680996</v>
       </c>
       <c r="B5" t="n">
-        <v>58046</v>
+        <v>58050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>125680994</v>
       </c>
       <c r="B6" t="n">
-        <v>58131</v>
+        <v>58135</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105931</v>
+        <v>105944</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 54875-2019 artfynd.xlsx
+++ b/artfynd/A 54875-2019 artfynd.xlsx
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125680976</v>
+        <v>125680996</v>
       </c>
       <c r="B4" t="n">
-        <v>91295</v>
+        <v>58050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5321</v>
+        <v>103037</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,23 +963,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -997,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125680996</v>
+        <v>125680976</v>
       </c>
       <c r="B5" t="n">
-        <v>58050</v>
+        <v>91295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103037</v>
+        <v>5321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,12 +1065,23 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 54875-2019 artfynd.xlsx
+++ b/artfynd/A 54875-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125681019</v>
       </c>
       <c r="B2" t="n">
-        <v>105296</v>
+        <v>105299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>125681044</v>
       </c>
       <c r="B3" t="n">
-        <v>105467</v>
+        <v>105470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,32 +884,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125680996</v>
+        <v>125680976</v>
       </c>
       <c r="B4" t="n">
-        <v>58050</v>
+        <v>91295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>5321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -963,12 +963,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -986,32 +997,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125680976</v>
+        <v>125680996</v>
       </c>
       <c r="B5" t="n">
-        <v>91295</v>
+        <v>58050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5321</v>
+        <v>103037</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,23 +1076,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
           <t>blandskog</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>aspkubbe</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1204,7 +1204,7 @@
         <v>125681081</v>
       </c>
       <c r="B7" t="n">
-        <v>105944</v>
+        <v>105947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
